--- a/artfynd/A 10755-2024 artfynd.xlsx
+++ b/artfynd/A 10755-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97381833</v>
+        <v>97381882</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,24 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -716,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529636.1947291726</v>
+        <v>529648</v>
       </c>
       <c r="R2" t="n">
-        <v>6706772.843896353</v>
+        <v>6706775</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97381882</v>
+        <v>104871280</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,17 +812,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -832,19 +831,20 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storsten , Dlr</t>
+          <t>Storsten, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529648.0192297903</v>
+        <v>529650</v>
       </c>
       <c r="R3" t="n">
-        <v>6706775.404589555</v>
+        <v>6706775</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +868,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-12-02</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-12-02</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,59 +897,83 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Låga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Yngve Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Yngve Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104871450</v>
+        <v>104871447</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -953,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529627.0730707661</v>
+        <v>529627</v>
       </c>
       <c r="R4" t="n">
-        <v>6706801.841690449</v>
+        <v>6706802</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1041,56 +1070,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104871385</v>
+        <v>97381833</v>
       </c>
       <c r="B5" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storsten, Dlr</t>
+          <t>Storsten , Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529645.6703015505</v>
+        <v>529637</v>
       </c>
       <c r="R5" t="n">
-        <v>6706881.326404709</v>
+        <v>6706773</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,22 +1136,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2021-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
+          <t>2021-12-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,34 +1160,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Yngve Johansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Yngve Johansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104871364</v>
+        <v>104871284</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,10 +1216,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529664.192519935</v>
+        <v>529650</v>
       </c>
       <c r="R6" t="n">
-        <v>6706789.334356841</v>
+        <v>6706775</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,7 +1251,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1261,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,9 +1284,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Låga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1288,15 +1309,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104871447</v>
+        <v>104871364</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,33 +1320,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1339,10 +1347,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529627.0730707661</v>
+        <v>529664</v>
       </c>
       <c r="R7" t="n">
-        <v>6706801.841690449</v>
+        <v>6706789</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1374,7 +1382,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1384,7 +1392,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,15 +1435,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104871284</v>
+        <v>104871453</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,10 +1473,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529649.9933443975</v>
+        <v>529627</v>
       </c>
       <c r="R8" t="n">
-        <v>6706775.420772674</v>
+        <v>6706802</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1505,7 +1508,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1515,7 +1518,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,14 +1541,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies # Låga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1563,15 +1561,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104871453</v>
+        <v>116045236</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,17 +1595,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storsten, Dlr</t>
+          <t>Storsten NV, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529627.0730707661</v>
+        <v>529662</v>
       </c>
       <c r="R9" t="n">
-        <v>6706801.841690449</v>
+        <v>6706782</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1636,22 +1629,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,45 +1647,25 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Yngve Johansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Yngve Johansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104871280</v>
+        <v>116045256</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,48 +1673,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storsten, Dlr</t>
+          <t>Storsten NV, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529649.9933443975</v>
+        <v>529650</v>
       </c>
       <c r="R10" t="n">
-        <v>6706775.420772674</v>
+        <v>6706774</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1775,27 +1730,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en låga</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1808,50 +1748,25 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies # Låga</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Yngve Johansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Yngve Johansson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116045256</v>
+        <v>104871450</v>
       </c>
       <c r="B11" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,21 +1774,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1882,17 +1797,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storsten NV, Dlr</t>
+          <t>Storsten, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529650</v>
+        <v>529627</v>
       </c>
       <c r="R11" t="n">
-        <v>6706774</v>
+        <v>6706802</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1916,12 +1831,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2022-11-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2022-11-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1934,15 +1859,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Yngve Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Yngve Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1952,12 +1892,7 @@
         <v>116045346</v>
       </c>
       <c r="B12" t="n">
-        <v>90960</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2068,37 +2003,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116045236</v>
+        <v>104871385</v>
       </c>
       <c r="B13" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2107,17 +2037,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storsten NV, Dlr</t>
+          <t>Storsten, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529662</v>
+        <v>529646</v>
       </c>
       <c r="R13" t="n">
-        <v>6706782</v>
+        <v>6706881</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2141,12 +2071,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2022-11-30</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2022-11-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,12 +2102,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Yngve Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Yngve Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 10755-2024 artfynd.xlsx
+++ b/artfynd/A 10755-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97381882</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -933,6 +943,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104871280</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1067,6 +1082,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104871447</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1175,6 +1195,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97381833</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1306,6 +1331,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104871284</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1432,6 +1462,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104871364</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1558,6 +1593,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104871453</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1659,6 +1699,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116045236</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1760,6 +1805,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116045256</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1886,6 +1936,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104871450</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2000,6 +2055,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116045346</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2111,8 +2171,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104871385</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>